--- a/model/GRG_model_v0.7.xlsx
+++ b/model/GRG_model_v0.7.xlsx
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="674">
   <si>
     <t xml:space="preserve">Greggs three-statement forecast model – Notes</t>
   </si>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">Variance</t>
   </si>
   <si>
-    <t xml:space="preserve">Test 1a structural back-test of the revenue method (0.4% gap); Test 2 live-test layout for Jan/Mar 2027.</t>
+    <t xml:space="preserve">Test 1: FY25 back-test of the revenue method (0.4% gap); Test 2: FY26 live-test layout for January/March 2027.</t>
   </si>
   <si>
     <t xml:space="preserve">Tax &amp; Audit</t>
@@ -1769,364 +1769,348 @@
     <t xml:space="preserve">Variance analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Test 1 (Phase 3): forecast FY25 using data up to FY24 only, then compare with actual FY25. Test 2 (Phase 4): locked FY26 forecast vs the January trading update and March results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 1: FY25 back-test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your FY25 forecast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual FY25</t>
+    <t xml:space="preserve">Two tests. Test 1 checks the revenue method on FY25 using Greggs' actual drivers. Test 2 checks the locked FY26 forecast against Greggs' own figures in January and March 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 1: FY25 back-test of the revenue method (FY24 base + Greggs' actual FY25 drivers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses Greggs' actual FY25 like-for-like growth and openings, so it tests the method, not my assumptions. Profit and cash lines are not back-tested: the model starts from FY25 actuals, so Test 2 covers them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24 company-managed revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 like-for-like growth (actual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24 sales per average shop (£m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 sales per mature shop (£m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY24 company-managed net openings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 company-managed net openings (actual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New-shop sales vs mature shop (your assumption)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-year effect of FY24 openings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 openings (half a year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method's FY25 company-managed revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual FY25 company-managed revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance (actual − method)</t>
   </si>
   <si>
     <t xml:space="preserve">Variance %</t>
   </si>
   <si>
-    <t xml:space="preserve">Explanation (one sentence each)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structural back-test (Test 1a below): the method fed Greggs' actual FY25 openings and LFL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue: B2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not back-tested: B2B, profit and cash lines start from FY25 actuals, so testing them on FY25 would need a separate FY24-based model. Test 2 (live test) covers them on FY26.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As above.</t>
+    <t xml:space="preserve">New-shop % that would explain all of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explanation (your words, Session D):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fed actual FY25 openings and LFL, the method undershot company-managed revenue by £8.4m (0.4%). The likely cause is the 50 relocations into bigger units, which add sales outside LFL that the method does not capture. New-shop sales stay at 85% because new openings are mostly smaller formats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 2: FY26 live test (lock the forecast before the January 2027 trading update)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locked FY26 forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual (Jan trading update / March results)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sales (£m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shops at year end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlying PBT (£m, March)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax &amp; Audit review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax rate reconciliation, current/deferred split and deferred tax roll-forward from the tax notes (FY21–FY25); the FY25 key audit matter mapped to the model; model controls. Charges are negative, as on the Historical sheet. Blue = typed from the reports; green = linked from Historical.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Tax rate reconciliation: why the effective rate differs from the UK rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source / note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK statutory corporation tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax note (FY23 note: 23.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax at the statutory rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Items not taxable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax note: FY24–25 AR25 p153; FY23 AR24 p152; FY22 AR23 p143; FY21 AR22 p132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Non-tax-deductible depreciation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Impact of change in deferred tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Adjustment for prior years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other (name it in a comment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax charge per reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax charge per income statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference (should be 0 once filled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective tax rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap to statutory rate (percentage points)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: feeds the Drivers adjustment row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Split of the tax charge: current vs deferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current tax charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current year + prior-year adjustments. FY25 AR25 p152; FY24 AR24 p151; FY23 AR23 p142; FY21–22 AR22 p131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deferred tax charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origination/reversal + prior-year adjustments (same pages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (should equal the income statement charge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memo: tax actually paid in cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical (cash flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Deferred tax liability roll-forward (shown as positive balances)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening deferred tax liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY21 opening = FY20 closing, AR21 p119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charged to the income statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deferred tax charge per the tax note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charged to other comprehensive income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not separately analysed here; included in 'other'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other movements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balancing figure: OCI (pensions), equity (share schemes) and other movements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing liability (calculated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing liability per balance sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memo: capex (PPE + intangibles, cash)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memo: depreciation of PPE + amortisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex in excess of depreciation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Key audit matter (FY25 independent auditor's report, AR25 PDF pp. 123–125) mapped to the model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key audit matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the auditor did</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How my model treats it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoverability of shop-based assets (IAS 36)
+• Right-of-use assets £413.0m and PPE £832.1m
+• Each shop is a cash-generating unit
+• FY25 impairment: £3.0m (ROU) + £3.9m (PPE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Challenged value-in-use assumptions: cash flows, discount rate, growth, cost inflation, central cost allocation
+• Sensitivity analysis on headroom
+• Used valuation and modelling specialists
+• Tested the accuracy of past forecasts
+• Materiality £8.01m; concluded management's view was appropriate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• No separate impairment line: the margin is based on FY22–FY25, which already absorbed £3–7m of impairments a year
+• The risk rises in the downside: weaker new-shop sales (70% of a mature shop) could push more shops below their book value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY25 had one key audit matter only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. Controls in my model: how I know the numbers are right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it checks and the result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Source check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scripts/verify_sources.py: all 352 testable historical figures are found on the report page they cite. 52 zeros and 3 derived figures are listed separately; 3 come from the Q4 trading update.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scripts/reconcile.py and the Checks tab: 13 checks rebuild operating profit, PBT, total and net assets, the balance sheet and cash movements, and tie to the reported totals in all five years. The tax checks on this tab are within £0.1m (report rounding).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Forecast integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The balance sheet balances and closing cash ties in FY26–FY28 in every scenario and in all 30,000 Monte Carlo run-years; the Python model matches the Excel base case to £0.0m.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monte Carlo simulation – 10,000 runs of the full three-statement model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated by simulation/monte_carlo.py (seed 42) from the Drivers tab ranges. Values, not live formulas: re-run the script after changing assumptions. Controls: the Python base case equals this workbook's base case to £0.0m, and the balance sheet balances in all 30,000 run-years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentiles (£m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closing cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 underlying PBT above FY25 (£171.9m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26 underlying PBT above the base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY28 underlying PBT above £200m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash falls below £50m in any year FY26–FY28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash falls below zero in any year FY26–FY28 (needs new borrowing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tornado: FY28 underlying PBT with one driver at its min / max (others at base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cash at min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cash at max</t>
   </si>
   <si>
     <t xml:space="preserve">Capex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2: FY26 live test (lock your forecast before the January 2027 trading update)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locked FY26 forecast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual (Jan trading update / March results)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total sales (£m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shops at year end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Underlying PBT (£m, March)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 1a: structural back-test of the revenue method (FY24 base + actual FY25 drivers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uses Greggs' actual FY25 LFL and openings, so it tests the method, not the assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24 company-managed revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25 like-for-like growth (actual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24 sales per average shop (£m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25 sales per mature shop (£m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY24 company-managed net openings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25 company-managed net openings (actual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New-shop sales vs mature shop (your assumption)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full-year effect of FY24 openings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY25 openings (half a year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Method's FY25 company-managed revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual FY25 company-managed revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance (actual − method)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New-shop % that would explain all of it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explanation (your words, Session D):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fed actual FY25 openings and LFL, the method undershot company-managed revenue by £8.4m (0.4%). The likely cause is the 50 relocations into bigger units, which add sales outside LFL that the method does not capture. New-shop sales stay at 85% because new openings are mostly smaller formats.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax &amp; Audit review (Phase 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill the yellow cells from the tax note and the auditor's report. Charges are negative, as on the Historical sheet. Green = linked from Historical. Checks at the bottom of the Checks tab turn on once you start filling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. Tax rate reconciliation: why the effective rate differs from the UK rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source / note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK statutory corporation tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax note (FY23 note: 23.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax at the statutory rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Items not taxable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax note: FY24–25 AR25 p153; FY23 AR24 p152; FY22 AR23 p143; FY21 AR22 p132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Non-tax-deductible depreciation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Impact of change in deferred tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Adjustment for prior years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other (name it in a comment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax charge per reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax charge per income statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference (should be 0 once filled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effective tax rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap to statutory rate (percentage points)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formula: feeds the Drivers adjustment row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. Split of the tax charge: current vs deferred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current tax charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current year + prior-year adjustments. FY25 AR25 p152; FY24 AR24 p151; FY23 AR23 p142; FY21–22 AR22 p131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deferred tax charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Origination/reversal + prior-year adjustments (same pages)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total (should equal the income statement charge)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memo: tax actually paid in cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical (cash flow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. Deferred tax liability roll-forward (shown as positive balances)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening deferred tax liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY21 opening = FY20 closing, AR21 p119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charged to the income statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deferred tax charge per the tax note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charged to other comprehensive income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not separately analysed here; included in 'other'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other movements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balancing figure: OCI (pensions), equity (share schemes) and other movements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing liability (calculated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing liability per balance sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memo: capex (PPE + intangibles, cash)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memo: depreciation of PPE + amortisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex in excess of depreciation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. Key audit matters (AR25 independent auditor's report, PDF pp. 123–125) mapped to the model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key audit matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What the auditor did (in brief)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model lines affected and how I treated them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoverability of shop-based assets (IAS 36): £413.0m right-of-use assets and £832.1m PPE; each shop is a cash-generating unit; FY25 impairment £3.0m (ROU) + £3.9m (PPE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Challenged value-in-use assumptions (cash flows, discount rate, growth, cost inflation, central cost allocation); sensitivity analysis on headroom; used valuation and modelling specialists; tested the accuracy of past forecasts. Materiality £8.01m. Concluded management's view appropriate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No separate impairment line: the margin assumption is based on FY22–FY25, which already absorbed £3–7m of impairments a year. The risk rises in the downside, where weaker new-shop sales (70%) could push more shops below their book value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(FY25 had one key audit matter only.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example of the level of detail (replace with your own, from the report): Impairment of shop assets | Tested the value-in-use model and its assumptions | Right-of-use assets and PPE; impairment kept inside underlying costs, see Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E. Controls in my model (how I know the numbers are right)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source check (scripts/verify_sources.py): all 352 testable historical figures are found on the report page they cite; 52 zeros and 3 derived figures are listed separately, and 3 come from the Q4 trading update.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconciliation (scripts/reconcile.py and the Checks tab): 13 checks rebuild operating profit, PBT, total and net assets, the balance sheet and cash movements and tie to the reported totals in all five years; the three tax checks above are within 0.1 (report rounding).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecast integrity: the balance sheet balances and closing cash ties in FY26–FY28 in every scenario and in all 30,000 Monte Carlo run-years; the Python model matches the Excel base case to £0.0m.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideas: source page for every typed figure; Checks tab ties totals to the reports; balance and cash checks on every forecast year; colour coding of inputs vs formulas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Carlo simulation – 10,000 runs of the full three-statement model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by simulation/monte_carlo.py (seed 42) from the Drivers tab ranges. Values, not live formulas: re-run the script after changing assumptions. Controls: the Python base case equals this workbook's base case to £0.0m, and the balance sheet balances in all 30,000 run-years.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentiles (£m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Question</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY26 underlying PBT above FY25 (£171.9m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY26 underlying PBT above the base case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY28 underlying PBT above £200m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash falls below £50m in any year FY26–FY28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash falls below zero in any year FY26–FY28 (needs new borrowing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tornado: FY28 underlying PBT with one driver at its min / max (others at base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cash at min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cash at max</t>
   </si>
   <si>
     <t xml:space="preserve">Your conclusions (Session E, in your own words)</t>
@@ -2412,13 +2396,13 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0"/>
     <numFmt numFmtId="174" formatCode="0.0;\(0.0\);0.0"/>
     <numFmt numFmtId="175" formatCode="0"/>
     <numFmt numFmtId="176" formatCode="\+#,##0.0;\−#,##0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2580,6 +2564,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="14"/>
       <name val="Arial"/>
@@ -2626,7 +2618,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -2639,6 +2631,21 @@
       <right/>
       <top style="thin"/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -2676,7 +2683,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="110">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2905,15 +2912,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2961,16 +2960,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2997,39 +2996,39 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3049,79 +3048,75 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3170,7 +3165,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -3228,9 +3223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591480</xdr:colOff>
+      <xdr:colOff>590760</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3244,7 +3239,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="570600"/>
-          <a:ext cx="6094800" cy="3199320"/>
+          <a:ext cx="6094080" cy="3198600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3265,9 +3260,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>591480</xdr:colOff>
+      <xdr:colOff>590760</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>7200</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3281,7 +3276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11466360" y="4190040"/>
-          <a:ext cx="6094800" cy="2894400"/>
+          <a:ext cx="6094080" cy="2893680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4035,7 +4030,7 @@
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
         <v>90</v>
       </c>
@@ -4049,7 +4044,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
         <v>93</v>
       </c>
@@ -4063,7 +4058,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
         <v>96</v>
       </c>
@@ -4077,7 +4072,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
         <v>99</v>
       </c>
@@ -4091,7 +4086,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
         <v>102</v>
       </c>
@@ -4105,7 +4100,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
         <v>105</v>
       </c>
@@ -4119,7 +4114,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
         <v>108</v>
       </c>
@@ -4133,7 +4128,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
         <v>111</v>
       </c>
@@ -4147,7 +4142,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
         <v>114</v>
       </c>
@@ -4161,7 +4156,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
         <v>117</v>
       </c>
@@ -4175,7 +4170,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
         <v>120</v>
       </c>
@@ -4189,7 +4184,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
         <v>123</v>
       </c>
@@ -4229,20 +4224,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>131</v>
@@ -4271,404 +4266,404 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="91" t="n">
+      <c r="C5" s="89" t="n">
         <f aca="false">ROUND(Historical!C13-Historical!C30,1)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="91" t="n">
+      <c r="D5" s="89" t="n">
         <f aca="false">ROUND(Historical!D13-Historical!D30,1)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="91" t="n">
+      <c r="E5" s="89" t="n">
         <f aca="false">ROUND(Historical!E13-Historical!E30,1)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="91" t="n">
+      <c r="F5" s="89" t="n">
         <f aca="false">ROUND(Historical!F13-Historical!F30,1)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="91" t="n">
+      <c r="G5" s="89" t="n">
         <f aca="false">ROUND(Historical!G13-Historical!G30,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="91" t="n">
+      <c r="C6" s="89" t="n">
         <f aca="false">ROUND(Historical!C16-Historical!C31,1)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="91" t="n">
+      <c r="D6" s="89" t="n">
         <f aca="false">ROUND(Historical!D16-Historical!D31,1)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="91" t="n">
+      <c r="E6" s="89" t="n">
         <f aca="false">ROUND(Historical!E16-Historical!E31,1)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="91" t="n">
+      <c r="F6" s="89" t="n">
         <f aca="false">ROUND(Historical!F16-Historical!F31,1)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="91" t="n">
+      <c r="G6" s="89" t="n">
         <f aca="false">ROUND(Historical!G16-Historical!G31,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="91" t="n">
+      <c r="C7" s="89" t="n">
         <f aca="false">ROUND(Historical!C18-Historical!C32,1)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="91" t="n">
+      <c r="D7" s="89" t="n">
         <f aca="false">ROUND(Historical!D18-Historical!D32,1)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="91" t="n">
+      <c r="E7" s="89" t="n">
         <f aca="false">ROUND(Historical!E18-Historical!E32,1)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="91" t="n">
+      <c r="F7" s="89" t="n">
         <f aca="false">ROUND(Historical!F18-Historical!F32,1)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="91" t="n">
+      <c r="G7" s="89" t="n">
         <f aca="false">ROUND(Historical!G18-Historical!G32,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="91" t="n">
+      <c r="C8" s="89" t="n">
         <f aca="false">ROUND(Historical!C25-Historical!C33,1)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="91" t="n">
+      <c r="D8" s="89" t="n">
         <f aca="false">ROUND(Historical!D25-Historical!D33,1)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="91" t="n">
+      <c r="E8" s="89" t="n">
         <f aca="false">ROUND(Historical!E25-Historical!E33,1)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="91" t="n">
+      <c r="F8" s="89" t="n">
         <f aca="false">ROUND(Historical!F25-Historical!F33,1)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="91" t="n">
+      <c r="G8" s="89" t="n">
         <f aca="false">ROUND(Historical!G25-Historical!G33,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="91" t="n">
+      <c r="C9" s="89" t="n">
         <f aca="false">ROUND(Historical!C36+Historical!C37-Historical!C7,1)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="91" t="n">
+      <c r="D9" s="89" t="n">
         <f aca="false">ROUND(Historical!D36+Historical!D37-Historical!D7,1)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="91" t="n">
+      <c r="E9" s="89" t="n">
         <f aca="false">ROUND(Historical!E36+Historical!E37-Historical!E7,1)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="91" t="n">
+      <c r="F9" s="89" t="n">
         <f aca="false">ROUND(Historical!F36+Historical!F37-Historical!F7,1)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="91" t="n">
+      <c r="G9" s="89" t="n">
         <f aca="false">ROUND(Historical!G36+Historical!G37-Historical!G7,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="91" t="n">
+      <c r="C10" s="89" t="n">
         <f aca="false">ROUND(Historical!C63-Historical!C83,1)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="91" t="n">
+      <c r="D10" s="89" t="n">
         <f aca="false">ROUND(Historical!D63-Historical!D83,1)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="91" t="n">
+      <c r="E10" s="89" t="n">
         <f aca="false">ROUND(Historical!E63-Historical!E83,1)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="91" t="n">
+      <c r="F10" s="89" t="n">
         <f aca="false">ROUND(Historical!F63-Historical!F83,1)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="91" t="n">
+      <c r="G10" s="89" t="n">
         <f aca="false">ROUND(Historical!G63-Historical!G83,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="91" t="n">
+      <c r="C11" s="89" t="n">
         <f aca="false">ROUND(Historical!C77-Historical!C84,1)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="91" t="n">
+      <c r="D11" s="89" t="n">
         <f aca="false">ROUND(Historical!D77-Historical!D84,1)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="91" t="n">
+      <c r="E11" s="89" t="n">
         <f aca="false">ROUND(Historical!E77-Historical!E84,1)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="91" t="n">
+      <c r="F11" s="89" t="n">
         <f aca="false">ROUND(Historical!F77-Historical!F84,1)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="91" t="n">
+      <c r="G11" s="89" t="n">
         <f aca="false">ROUND(Historical!G77-Historical!G84,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="C12" s="91" t="n">
+        <v>601</v>
+      </c>
+      <c r="C12" s="89" t="n">
         <f aca="false">ROUND(Historical!C77-Historical!C82,1)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="91" t="n">
+      <c r="D12" s="89" t="n">
         <f aca="false">ROUND(Historical!D77-Historical!D82,1)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="91" t="n">
+      <c r="E12" s="89" t="n">
         <f aca="false">ROUND(Historical!E77-Historical!E82,1)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="91" t="n">
+      <c r="F12" s="89" t="n">
         <f aca="false">ROUND(Historical!F77-Historical!F82,1)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="91" t="n">
+      <c r="G12" s="89" t="n">
         <f aca="false">ROUND(Historical!G77-Historical!G82,1)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="91" t="n">
+      <c r="H12" s="89" t="n">
         <f aca="false">ROUND(Forecast!H77-Forecast!H82,1)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="91" t="n">
+      <c r="I12" s="89" t="n">
         <f aca="false">ROUND(Forecast!I77-Forecast!I82,1)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="91" t="n">
+      <c r="J12" s="89" t="n">
         <f aca="false">ROUND(Forecast!J77-Forecast!J82,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="C13" s="91" t="n">
+        <v>601</v>
+      </c>
+      <c r="C13" s="89" t="n">
         <f aca="false">ROUND(Historical!C113-Historical!C61,1)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="91" t="n">
+      <c r="D13" s="89" t="n">
         <f aca="false">ROUND(Historical!D113-Historical!D61,1)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="91" t="n">
+      <c r="E13" s="89" t="n">
         <f aca="false">ROUND(Historical!E113-Historical!E61,1)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="91" t="n">
+      <c r="F13" s="89" t="n">
         <f aca="false">ROUND(Historical!F113-Historical!F61,1)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="91" t="n">
+      <c r="G13" s="89" t="n">
         <f aca="false">ROUND(Historical!G113-Historical!G61,1)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="91" t="n">
+      <c r="H13" s="89" t="n">
         <f aca="false">ROUND(Forecast!H113-Forecast!H61,1)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="91" t="n">
+      <c r="I13" s="89" t="n">
         <f aca="false">ROUND(Forecast!I113-Forecast!I61,1)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="91" t="n">
+      <c r="J13" s="89" t="n">
         <f aca="false">ROUND(Forecast!J113-Forecast!J61,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="91" t="n">
+      <c r="C14" s="89" t="n">
         <f aca="false">ROUND(Historical!C111-Historical!C114,1)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="91" t="n">
+      <c r="D14" s="89" t="n">
         <f aca="false">ROUND(Historical!D111-Historical!D114,1)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="91" t="n">
+      <c r="E14" s="89" t="n">
         <f aca="false">ROUND(Historical!E111-Historical!E114,1)</f>
         <v>-0</v>
       </c>
-      <c r="F14" s="91" t="n">
+      <c r="F14" s="89" t="n">
         <f aca="false">ROUND(Historical!F111-Historical!F114,1)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="91" t="n">
+      <c r="G14" s="89" t="n">
         <f aca="false">ROUND(Historical!G111-Historical!G114,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="91" t="n">
+      <c r="C15" s="89" t="n">
         <f aca="false">ROUND(Historical!C138-Historical!C92,1)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="91" t="n">
+      <c r="D15" s="89" t="n">
         <f aca="false">ROUND(Historical!D138-Historical!D92,1)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="91" t="n">
+      <c r="E15" s="89" t="n">
         <f aca="false">ROUND(Historical!E138-Historical!E92,1)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="91" t="n">
+      <c r="F15" s="89" t="n">
         <f aca="false">ROUND(Historical!F138-Historical!F92,1)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="91" t="n">
+      <c r="G15" s="89" t="n">
         <f aca="false">ROUND(Historical!G138-Historical!G92,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="91" t="n">
+      <c r="C16" s="89" t="n">
         <f aca="false">ROUND(Historical!C121-Historical!C18,1)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="91" t="n">
+      <c r="D16" s="89" t="n">
         <f aca="false">ROUND(Historical!D121-Historical!D18,1)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="91" t="n">
+      <c r="E16" s="89" t="n">
         <f aca="false">ROUND(Historical!E121-Historical!E18,1)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="91" t="n">
+      <c r="F16" s="89" t="n">
         <f aca="false">ROUND(Historical!F121-Historical!F18,1)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="91" t="n">
+      <c r="G16" s="89" t="n">
         <f aca="false">ROUND(Historical!G121-Historical!G18,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="91" t="n">
+      <c r="C17" s="89" t="n">
         <f aca="false">ROUND(Historical!C46,1)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="91" t="n">
+      <c r="D17" s="89" t="n">
         <f aca="false">ROUND(Historical!D46,1)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="91" t="n">
+      <c r="E17" s="89" t="n">
         <f aca="false">ROUND(Historical!E46,1)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="91" t="n">
+      <c r="F17" s="89" t="n">
         <f aca="false">ROUND(Historical!F46,1)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="91" t="n">
+      <c r="G17" s="89" t="n">
         <f aca="false">ROUND(Historical!G46,1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" s="92" t="n">
+        <v>607</v>
+      </c>
+      <c r="C19" s="90" t="n">
         <f aca="false">SUMPRODUCT(ABS(C5:G17))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C20" s="27" t="str">
         <f aca="false">IF(C19&lt;0.05,"OK","CHECK")</f>
@@ -4677,194 +4672,194 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="91" t="n">
+      <c r="C23" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C9:C13)=0,"",IF(ABS('Tax &amp; Audit'!C16)&lt;0.15,0,ROUND('Tax &amp; Audit'!C16,1)))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="91" t="n">
+      <c r="D23" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D9:D13)=0,"",IF(ABS('Tax &amp; Audit'!D16)&lt;0.15,0,ROUND('Tax &amp; Audit'!D16,1)))</f>
         <v>0</v>
       </c>
-      <c r="E23" s="91" t="n">
+      <c r="E23" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E9:E13)=0,"",IF(ABS('Tax &amp; Audit'!E16)&lt;0.15,0,ROUND('Tax &amp; Audit'!E16,1)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="91" t="n">
+      <c r="F23" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F9:F13)=0,"",IF(ABS('Tax &amp; Audit'!F16)&lt;0.15,0,ROUND('Tax &amp; Audit'!F16,1)))</f>
         <v>0</v>
       </c>
-      <c r="G23" s="91" t="n">
+      <c r="G23" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G9:G13)=0,"",IF(ABS('Tax &amp; Audit'!G16)&lt;0.15,0,ROUND('Tax &amp; Audit'!G16,1)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="91" t="n">
+      <c r="C24" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C22:C23)=0,"",ROUND('Tax &amp; Audit'!C25,1))</f>
         <v>0</v>
       </c>
-      <c r="D24" s="91" t="n">
+      <c r="D24" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D22:D23)=0,"",ROUND('Tax &amp; Audit'!D25,1))</f>
         <v>0</v>
       </c>
-      <c r="E24" s="91" t="n">
+      <c r="E24" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E22:E23)=0,"",ROUND('Tax &amp; Audit'!E25,1))</f>
         <v>0</v>
       </c>
-      <c r="F24" s="91" t="n">
+      <c r="F24" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F22:F23)=0,"",ROUND('Tax &amp; Audit'!F25,1))</f>
         <v>0</v>
       </c>
-      <c r="G24" s="91" t="n">
+      <c r="G24" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G22:G23)=0,"",ROUND('Tax &amp; Audit'!G25,1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="91" t="n">
+      <c r="C25" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!C31:C33)=0,"",ROUND('Tax &amp; Audit'!C36,1))</f>
         <v>0</v>
       </c>
-      <c r="D25" s="91" t="n">
+      <c r="D25" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!D31:D33)=0,"",ROUND('Tax &amp; Audit'!D36,1))</f>
         <v>0</v>
       </c>
-      <c r="E25" s="91" t="n">
+      <c r="E25" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!E31:E33)=0,"",ROUND('Tax &amp; Audit'!E36,1))</f>
         <v>0</v>
       </c>
-      <c r="F25" s="91" t="n">
+      <c r="F25" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!F31:F33)=0,"",ROUND('Tax &amp; Audit'!F36,1))</f>
         <v>0</v>
       </c>
-      <c r="G25" s="91" t="n">
+      <c r="G25" s="89" t="n">
         <f aca="false">IF(COUNT('Tax &amp; Audit'!G31:G33)=0,"",ROUND('Tax &amp; Audit'!G36,1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="46" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="s">
-        <v>622</v>
-      </c>
-      <c r="B29" s="64" t="s">
-        <v>623</v>
+        <v>614</v>
+      </c>
+      <c r="B29" s="62" t="s">
+        <v>615</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>628</v>
+        <v>619</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>620</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>628</v>
+        <v>619</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>620</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>628</v>
+        <v>625</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>620</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="C33" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>620</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>628</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>628</v>
+        <v>619</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>620</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="C35" s="57" t="s">
-        <v>628</v>
+        <v>619</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>620</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -4912,306 +4907,306 @@
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="93" t="s">
-        <v>642</v>
-      </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
+      <c r="A2" s="71" t="s">
+        <v>634</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="46"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="94" t="s">
-        <v>643</v>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="91" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="86" t="s">
-        <v>644</v>
-      </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
+      <c r="A5" s="92" t="s">
+        <v>636</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="95" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="96" t="s">
+      <c r="A7" s="91" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="93" t="s">
         <v>366</v>
       </c>
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="D8" s="97" t="s">
+      <c r="D8" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="98" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57" t="s">
+      <c r="E8" s="94"/>
+      <c r="F8" s="95" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="99" t="n">
+      <c r="B9" s="96" t="n">
         <f aca="false">Scenarios!C7</f>
         <v>105</v>
       </c>
-      <c r="C9" s="99" t="n">
+      <c r="C9" s="96" t="n">
         <f aca="false">Scenarios!C8</f>
         <v>110</v>
       </c>
-      <c r="D9" s="99" t="n">
+      <c r="D9" s="96" t="n">
         <f aca="false">Scenarios!C9</f>
         <v>110</v>
       </c>
-      <c r="E9" s="100"/>
+      <c r="E9" s="97"/>
       <c r="F9" s="14" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="57" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="101" t="n">
+      <c r="B10" s="98" t="n">
         <f aca="false">Drivers!C7</f>
         <v>0.63</v>
       </c>
-      <c r="C10" s="101" t="n">
+      <c r="C10" s="98" t="n">
         <f aca="false">Drivers!D7</f>
         <v>0.63</v>
       </c>
-      <c r="D10" s="101" t="n">
+      <c r="D10" s="98" t="n">
         <f aca="false">Drivers!E7</f>
         <v>0.63</v>
       </c>
-      <c r="E10" s="102"/>
+      <c r="E10" s="99"/>
       <c r="F10" s="14" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="B11" s="103" t="n">
+      <c r="B11" s="100" t="n">
         <f aca="false">Scenarios!C10</f>
         <v>0.026</v>
       </c>
-      <c r="C11" s="103" t="n">
+      <c r="C11" s="100" t="n">
         <f aca="false">Scenarios!C11</f>
         <v>0.03</v>
       </c>
-      <c r="D11" s="103" t="n">
+      <c r="D11" s="100" t="n">
         <f aca="false">Scenarios!C12</f>
         <v>0.03</v>
       </c>
-      <c r="E11" s="104"/>
+      <c r="E11" s="101"/>
       <c r="F11" s="14" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="57" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="101" t="n">
+      <c r="B12" s="98" t="n">
         <f aca="false">Scenarios!C13</f>
         <v>0.85</v>
       </c>
-      <c r="C12" s="101" t="n">
+      <c r="C12" s="98" t="n">
         <f aca="false">Scenarios!C14</f>
         <v>0.85</v>
       </c>
-      <c r="D12" s="101" t="n">
+      <c r="D12" s="98" t="n">
         <f aca="false">Scenarios!C15</f>
         <v>0.85</v>
       </c>
-      <c r="E12" s="102"/>
+      <c r="E12" s="99"/>
       <c r="F12" s="14" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="57" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="44" t="s">
         <v>471</v>
       </c>
-      <c r="B13" s="103" t="n">
+      <c r="B13" s="100" t="n">
         <f aca="false">Scenarios!C16</f>
         <v>0.1</v>
       </c>
-      <c r="C13" s="103" t="n">
+      <c r="C13" s="100" t="n">
         <f aca="false">Scenarios!C17</f>
         <v>0.08</v>
       </c>
-      <c r="D13" s="103" t="n">
+      <c r="D13" s="100" t="n">
         <f aca="false">Scenarios!C18</f>
         <v>0.08</v>
       </c>
-      <c r="E13" s="104"/>
+      <c r="E13" s="101"/>
       <c r="F13" s="14" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="57" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="103" t="n">
+      <c r="B14" s="100" t="n">
         <f aca="false">Scenarios!C19</f>
         <v>0.088</v>
       </c>
-      <c r="C14" s="103" t="n">
+      <c r="C14" s="100" t="n">
         <f aca="false">Scenarios!C20</f>
         <v>0.09</v>
       </c>
-      <c r="D14" s="103" t="n">
+      <c r="D14" s="100" t="n">
         <f aca="false">Scenarios!C21</f>
         <v>0.093</v>
       </c>
-      <c r="E14" s="104"/>
+      <c r="E14" s="101"/>
       <c r="F14" s="14" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>653</v>
-      </c>
-      <c r="B15" s="105" t="n">
+        <v>645</v>
+      </c>
+      <c r="B15" s="75" t="n">
         <f aca="false">Drivers!C15</f>
         <v>180</v>
       </c>
-      <c r="C15" s="105" t="n">
+      <c r="C15" s="75" t="n">
         <f aca="false">Drivers!D15</f>
         <v>165</v>
       </c>
-      <c r="D15" s="105" t="n">
+      <c r="D15" s="75" t="n">
         <f aca="false">Drivers!E15</f>
         <v>160</v>
       </c>
-      <c r="E15" s="106"/>
+      <c r="E15" s="102"/>
       <c r="F15" s="14" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="57" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="103" t="n">
+      <c r="B16" s="100" t="n">
         <f aca="false">Drivers!C18</f>
         <v>0.26</v>
       </c>
-      <c r="C16" s="103" t="n">
+      <c r="C16" s="100" t="n">
         <f aca="false">Drivers!D18</f>
         <v>0.26</v>
       </c>
-      <c r="D16" s="103" t="n">
+      <c r="D16" s="100" t="n">
         <f aca="false">Drivers!E18</f>
         <v>0.26</v>
       </c>
-      <c r="E16" s="104"/>
+      <c r="E16" s="101"/>
       <c r="F16" s="14" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="86" t="s">
-        <v>656</v>
-      </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
+      <c r="A17" s="92" t="s">
+        <v>648</v>
+      </c>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="95" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="96" t="s">
+      <c r="A19" s="91" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="97" t="s">
-        <v>658</v>
-      </c>
-      <c r="C20" s="97" t="s">
+      <c r="B20" s="94" t="s">
+        <v>650</v>
+      </c>
+      <c r="C20" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="D20" s="97" t="s">
+      <c r="D20" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="F20" s="98"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="57" t="s">
+      <c r="F20" s="95"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="107" t="n">
+      <c r="B21" s="103" t="n">
         <f aca="false">Forecast!G7</f>
         <v>2151.2</v>
       </c>
-      <c r="C21" s="107" t="n">
+      <c r="C21" s="103" t="n">
         <f aca="false">Forecast!H7</f>
         <v>2283.5839018927</v>
       </c>
-      <c r="D21" s="107" t="n">
+      <c r="D21" s="103" t="n">
         <f aca="false">Forecast!I7</f>
         <v>2421.09999766661</v>
       </c>
-      <c r="E21" s="107" t="n">
+      <c r="E21" s="103" t="n">
         <f aca="false">Forecast!J7</f>
         <v>2566.82869963056</v>
       </c>
       <c r="F21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="57" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="107" t="n">
+      <c r="B22" s="103" t="n">
         <f aca="false">Forecast!G24</f>
         <v>187.5</v>
       </c>
-      <c r="C22" s="107" t="n">
+      <c r="C22" s="103" t="n">
         <f aca="false">Forecast!H24</f>
         <v>200.955383366558</v>
       </c>
-      <c r="D22" s="107" t="n">
+      <c r="D22" s="103" t="n">
         <f aca="false">Forecast!I24</f>
         <v>217.898999789995</v>
       </c>
-      <c r="E22" s="107" t="n">
+      <c r="E22" s="103" t="n">
         <f aca="false">Forecast!J24</f>
         <v>238.715069065642</v>
       </c>
@@ -5221,85 +5216,85 @@
       <c r="A23" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="B23" s="107" t="n">
+      <c r="B23" s="103" t="n">
         <f aca="false">Forecast!G25</f>
         <v>171.9</v>
       </c>
-      <c r="C23" s="107" t="n">
+      <c r="C23" s="103" t="n">
         <f aca="false">Forecast!H25</f>
         <v>180.238983366558</v>
       </c>
-      <c r="D23" s="107" t="n">
+      <c r="D23" s="103" t="n">
         <f aca="false">Forecast!I25</f>
         <v>196.941531546303</v>
       </c>
-      <c r="E23" s="107" t="n">
+      <c r="E23" s="103" t="n">
         <f aca="false">Forecast!J25</f>
         <v>217.63616146699</v>
       </c>
       <c r="F23" s="14"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="57" t="s">
-        <v>659</v>
-      </c>
-      <c r="B24" s="107" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="B24" s="103" t="n">
         <f aca="false">Forecast!G16</f>
         <v>167.4</v>
       </c>
-      <c r="C24" s="107" t="n">
+      <c r="C24" s="103" t="n">
         <f aca="false">Forecast!H16</f>
         <v>135.238983366558</v>
       </c>
-      <c r="D24" s="107" t="n">
+      <c r="D24" s="103" t="n">
         <f aca="false">Forecast!I16</f>
         <v>186.941531546303</v>
       </c>
-      <c r="E24" s="107" t="n">
+      <c r="E24" s="103" t="n">
         <f aca="false">Forecast!J16</f>
         <v>212.63616146699</v>
       </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="B25" s="107" t="n">
+      <c r="B25" s="103" t="n">
         <f aca="false">Forecast!G118</f>
         <v>-11.7</v>
       </c>
-      <c r="C25" s="107" t="n">
+      <c r="C25" s="103" t="n">
         <f aca="false">Forecast!H118</f>
         <v>84.552805073007</v>
       </c>
-      <c r="D25" s="107" t="n">
+      <c r="D25" s="103" t="n">
         <f aca="false">Forecast!I118</f>
         <v>91.0074838972138</v>
       </c>
-      <c r="E25" s="107" t="n">
+      <c r="E25" s="103" t="n">
         <f aca="false">Forecast!J118</f>
         <v>134.56925275289</v>
       </c>
       <c r="F25" s="14"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="57" t="s">
-        <v>484</v>
-      </c>
-      <c r="B26" s="107" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="44" t="s">
+        <v>569</v>
+      </c>
+      <c r="B26" s="103" t="n">
         <f aca="false">Forecast!G61</f>
         <v>70.8</v>
       </c>
-      <c r="C26" s="107" t="n">
+      <c r="C26" s="103" t="n">
         <f aca="false">Forecast!H61</f>
         <v>85.041805073007</v>
       </c>
-      <c r="D26" s="107" t="n">
+      <c r="D26" s="103" t="n">
         <f aca="false">Forecast!I61</f>
         <v>104.332068970221</v>
       </c>
-      <c r="E26" s="107" t="n">
+      <c r="E26" s="103" t="n">
         <f aca="false">Forecast!J61</f>
         <v>165.749757323111</v>
       </c>
@@ -5309,399 +5304,399 @@
       <c r="A27" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="103" t="n">
+      <c r="B27" s="100" t="n">
         <f aca="false">Forecast!G26</f>
         <v>0.0871606545184083</v>
       </c>
-      <c r="C27" s="103" t="n">
+      <c r="C27" s="100" t="n">
         <f aca="false">Forecast!H26</f>
         <v>0.0880000000000001</v>
       </c>
-      <c r="D27" s="103" t="n">
+      <c r="D27" s="100" t="n">
         <f aca="false">Forecast!I26</f>
         <v>0.09</v>
       </c>
-      <c r="E27" s="103" t="n">
+      <c r="E27" s="100" t="n">
         <f aca="false">Forecast!J26</f>
         <v>0.0929999999999999</v>
       </c>
       <c r="F27" s="14"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="94" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="96" t="s">
-        <v>661</v>
-      </c>
-      <c r="B30" s="97" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="91" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="93" t="s">
+        <v>653</v>
+      </c>
+      <c r="B30" s="94" t="s">
         <v>469</v>
       </c>
-      <c r="C30" s="97" t="s">
+      <c r="C30" s="94" t="s">
         <v>467</v>
       </c>
-      <c r="D30" s="97" t="s">
+      <c r="D30" s="94" t="s">
         <v>468</v>
       </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98" t="s">
-        <v>662</v>
+      <c r="E30" s="94"/>
+      <c r="F30" s="95" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="B31" s="108" t="n">
+      <c r="B31" s="104" t="n">
         <v>162.8</v>
       </c>
-      <c r="C31" s="107" t="n">
+      <c r="C31" s="103" t="n">
         <f aca="false">Forecast!H25</f>
         <v>180.238983366558</v>
       </c>
-      <c r="D31" s="108" t="n">
+      <c r="D31" s="104" t="n">
         <v>197.4</v>
       </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="83" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57" t="s">
+      <c r="E31" s="105"/>
+      <c r="F31" s="106" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="B32" s="108" t="n">
+      <c r="B32" s="104" t="n">
         <v>172.5</v>
       </c>
-      <c r="C32" s="107" t="n">
+      <c r="C32" s="103" t="n">
         <f aca="false">Forecast!J25</f>
         <v>217.63616146699</v>
       </c>
-      <c r="D32" s="108" t="n">
+      <c r="D32" s="104" t="n">
         <v>265</v>
       </c>
-      <c r="E32" s="109"/>
+      <c r="E32" s="105"/>
       <c r="F32" s="14"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="57" t="s">
-        <v>664</v>
-      </c>
-      <c r="B33" s="108" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="44" t="s">
+        <v>656</v>
+      </c>
+      <c r="B33" s="104" t="n">
         <v>56.6</v>
       </c>
-      <c r="C33" s="107" t="n">
+      <c r="C33" s="103" t="n">
         <f aca="false">MIN(Forecast!H61:J61)</f>
         <v>85.041805073007</v>
       </c>
-      <c r="D33" s="108" t="n">
+      <c r="D33" s="104" t="n">
         <v>100.2</v>
       </c>
-      <c r="E33" s="109"/>
+      <c r="E33" s="105"/>
       <c r="F33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="96" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="93" t="s">
+        <v>657</v>
+      </c>
+      <c r="B34" s="94" t="s">
+        <v>562</v>
+      </c>
+      <c r="C34" s="94" t="s">
+        <v>564</v>
+      </c>
+      <c r="D34" s="94" t="s">
+        <v>566</v>
+      </c>
+      <c r="E34" s="94"/>
+      <c r="F34" s="95"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="44" t="s">
+        <v>658</v>
+      </c>
+      <c r="B35" s="104" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="C35" s="104" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="D35" s="104" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="44" t="s">
+        <v>659</v>
+      </c>
+      <c r="B36" s="104" t="n">
+        <v>193</v>
+      </c>
+      <c r="C36" s="104" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="D36" s="104" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="E36" s="105"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="92" t="s">
+        <v>660</v>
+      </c>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="91" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>283</v>
+      </c>
+      <c r="C40" s="94" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="94" t="s">
+        <v>285</v>
+      </c>
+      <c r="E40" s="94"/>
+      <c r="F40" s="95"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="44" t="s">
+        <v>662</v>
+      </c>
+      <c r="B41" s="107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C41" s="107" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D41" s="107" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E41" s="108"/>
+      <c r="F41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="44" t="s">
+        <v>663</v>
+      </c>
+      <c r="B42" s="107" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C42" s="107" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="D42" s="107" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E42" s="108"/>
+      <c r="F42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="44" t="s">
+        <v>664</v>
+      </c>
+      <c r="B43" s="107" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C43" s="107" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D43" s="107" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E43" s="108"/>
+      <c r="F43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="44" t="s">
         <v>665</v>
       </c>
-      <c r="B34" s="97" t="s">
-        <v>572</v>
-      </c>
-      <c r="C34" s="97" t="s">
-        <v>574</v>
-      </c>
-      <c r="D34" s="97" t="s">
-        <v>576</v>
-      </c>
-      <c r="E34" s="97"/>
-      <c r="F34" s="98"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="57" t="s">
+      <c r="B44" s="107" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="C44" s="107" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="D44" s="107" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="E44" s="108"/>
+      <c r="F44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="92" t="s">
         <v>666</v>
       </c>
-      <c r="B35" s="108" t="n">
-        <v>169.8</v>
-      </c>
-      <c r="C35" s="108" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="D35" s="108" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="E35" s="109"/>
-      <c r="F35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="57" t="s">
+      <c r="B45" s="92"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="92"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="91" t="s">
         <v>667</v>
       </c>
-      <c r="B36" s="108" t="n">
-        <v>193</v>
-      </c>
-      <c r="C36" s="108" t="n">
-        <v>216.1</v>
-      </c>
-      <c r="D36" s="108" t="n">
-        <v>239.6</v>
-      </c>
-      <c r="E36" s="109"/>
-      <c r="F36" s="14"/>
-    </row>
-    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="86" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="94" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="94"/>
+      <c r="F48" s="95"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B49" s="103" t="n">
+        <f aca="false">Variance!B16</f>
+        <v>1888.77225035014</v>
+      </c>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="B50" s="103" t="n">
+        <f aca="false">Variance!B17</f>
+        <v>1897.2</v>
+      </c>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="B51" s="100" t="n">
+        <f aca="false">Variance!B19</f>
+        <v>0.00444220411652079</v>
+      </c>
+      <c r="C51" s="101"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="101"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="44" t="s">
+        <v>489</v>
+      </c>
+      <c r="B52" s="98" t="n">
+        <f aca="false">Variance!B20</f>
+        <v>0.961388985373251</v>
+      </c>
+      <c r="C52" s="99"/>
+      <c r="D52" s="99"/>
+      <c r="E52" s="99"/>
+      <c r="F52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="92" t="s">
         <v>668</v>
       </c>
-      <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="86"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="94" t="s">
+      <c r="B53" s="92"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="92"/>
+      <c r="E53" s="92"/>
+      <c r="F53" s="92"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="91" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="96" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="97" t="s">
-        <v>283</v>
-      </c>
-      <c r="C40" s="97" t="s">
-        <v>284</v>
-      </c>
-      <c r="D40" s="97" t="s">
-        <v>285</v>
-      </c>
-      <c r="E40" s="97"/>
-      <c r="F40" s="98"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="57" t="s">
+    <row r="56" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="92" t="s">
         <v>670</v>
       </c>
-      <c r="B41" s="110" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C41" s="110" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D41" s="110" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E41" s="111"/>
-      <c r="F41" s="14"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="57" t="s">
+      <c r="B56" s="92"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="91" t="s">
         <v>671</v>
       </c>
-      <c r="B42" s="110" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C42" s="110" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="D42" s="110" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="E42" s="111"/>
-      <c r="F42" s="14"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="57" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="92" t="s">
         <v>672</v>
       </c>
-      <c r="B43" s="110" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="C43" s="110" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="D43" s="110" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E43" s="111"/>
-      <c r="F43" s="14"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="57" t="s">
+      <c r="B59" s="92"/>
+      <c r="C59" s="92"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="91" t="s">
         <v>673</v>
       </c>
-      <c r="B44" s="110" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="C44" s="110" t="n">
-        <v>-24.7</v>
-      </c>
-      <c r="D44" s="110" t="n">
-        <v>-26.7</v>
-      </c>
-      <c r="E44" s="111"/>
-      <c r="F44" s="14"/>
-    </row>
-    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="86" t="s">
-        <v>674</v>
-      </c>
-      <c r="B45" s="86"/>
-      <c r="C45" s="86"/>
-      <c r="D45" s="86"/>
-      <c r="E45" s="86"/>
-      <c r="F45" s="86"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="94" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="96" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="97" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="97"/>
-      <c r="D48" s="97"/>
-      <c r="E48" s="97"/>
-      <c r="F48" s="98"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="B49" s="107" t="n">
-        <f aca="false">Variance!B36</f>
-        <v>1888.77225035014</v>
-      </c>
-      <c r="C49" s="109"/>
-      <c r="D49" s="109"/>
-      <c r="E49" s="109"/>
-      <c r="F49" s="14"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57" t="s">
-        <v>504</v>
-      </c>
-      <c r="B50" s="107" t="n">
-        <f aca="false">Variance!B37</f>
-        <v>1897.2</v>
-      </c>
-      <c r="C50" s="109"/>
-      <c r="D50" s="109"/>
-      <c r="E50" s="109"/>
-      <c r="F50" s="14"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57" t="s">
-        <v>477</v>
-      </c>
-      <c r="B51" s="103" t="n">
-        <f aca="false">Variance!B39</f>
-        <v>0.00444220411652079</v>
-      </c>
-      <c r="C51" s="104"/>
-      <c r="D51" s="104"/>
-      <c r="E51" s="104"/>
-      <c r="F51" s="14"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="57" t="s">
-        <v>506</v>
-      </c>
-      <c r="B52" s="101" t="n">
-        <f aca="false">Variance!B40</f>
-        <v>0.961388985373251</v>
-      </c>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="102"/>
-      <c r="F52" s="14"/>
-    </row>
-    <row r="53" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="86" t="s">
-        <v>676</v>
-      </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="94" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="86" t="s">
-        <v>678</v>
-      </c>
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="94" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="86" t="s">
-        <v>680</v>
-      </c>
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="94" t="s">
-        <v>681</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="112" t="str">
+      <c r="A62" s="109" t="str">
         <f aca="false">Simulation!B40</f>
         <v>In 90% of 10,000 runs FY26 underlying profit beats FY25's £172m, with a likely range of £170–190m, so I am confident profit grows.</v>
       </c>
-      <c r="B62" s="112"/>
-      <c r="C62" s="112"/>
-      <c r="D62" s="112"/>
-      <c r="E62" s="112"/>
-      <c r="F62" s="112"/>
+      <c r="B62" s="109"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="112" t="str">
+      <c r="A63" s="109" t="str">
         <f aca="false">Simulation!B41</f>
         <v>Cash stays positive in every run and falls below £50m in only 1%: with capex falling, Greggs can fund openings, restructuring and dividends without new debt, after negative free cash flow in FY25.</v>
       </c>
-      <c r="B63" s="112"/>
-      <c r="C63" s="112"/>
-      <c r="D63" s="112"/>
-      <c r="E63" s="112"/>
-      <c r="F63" s="112"/>
+      <c r="B63" s="109"/>
+      <c r="C63" s="109"/>
+      <c r="D63" s="109"/>
+      <c r="E63" s="109"/>
+      <c r="F63" s="109"/>
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="112" t="str">
+      <c r="A64" s="109" t="str">
         <f aca="false">Simulation!B42</f>
         <v>I would watch like-for-like growth: margin moves profit most (£53m), but LFL moves it £23m directly, pulls margin with it through operating leverage, and is the trend that has slowed from 18% to 2%.</v>
       </c>
-      <c r="B64" s="112"/>
-      <c r="C64" s="112"/>
-      <c r="D64" s="112"/>
-      <c r="E64" s="112"/>
-      <c r="F64" s="112"/>
+      <c r="B64" s="109"/>
+      <c r="C64" s="109"/>
+      <c r="D64" s="109"/>
+      <c r="E64" s="109"/>
+      <c r="F64" s="109"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -14691,23 +14686,23 @@
         <v>432</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="57" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="44" t="s">
         <v>433</v>
       </c>
-      <c r="B36" s="57" t="s">
+      <c r="B36" s="44" t="s">
         <v>379</v>
       </c>
-      <c r="C36" s="58" t="n">
+      <c r="C36" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="D36" s="58" t="n">
+      <c r="D36" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="E36" s="58" t="n">
+      <c r="E36" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="L36" s="59" t="s">
+      <c r="L36" s="56" t="s">
         <v>434</v>
       </c>
     </row>
@@ -14734,11 +14729,11 @@
       <c r="B38" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="C38" s="60" t="n">
+      <c r="C38" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
       <c r="L38" s="18" t="s">
         <v>438</v>
       </c>
@@ -14750,11 +14745,11 @@
       <c r="B39" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="C39" s="60" t="n">
+      <c r="C39" s="58" t="n">
         <v>0.3</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
       <c r="L39" s="18" t="s">
         <v>440</v>
       </c>
@@ -15067,7 +15062,7 @@
       <c r="A59" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="C59" s="61" t="s">
+      <c r="C59" s="59" t="s">
         <v>457</v>
       </c>
       <c r="L59" s="18" t="s">
@@ -15144,7 +15139,7 @@
       <c r="A4" s="46" t="s">
         <v>465</v>
       </c>
-      <c r="B4" s="62" t="n">
+      <c r="B4" s="60" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="str">
@@ -15153,89 +15148,89 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="61" t="s">
         <v>366</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="61" t="s">
         <v>466</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="61" t="s">
         <v>467</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="61" t="s">
         <v>468</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="61" t="s">
         <v>469</v>
       </c>
-      <c r="F6" s="63" t="s">
+      <c r="F6" s="61" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="63" t="s">
         <v>283</v>
       </c>
-      <c r="C7" s="66" t="n">
+      <c r="C7" s="64" t="n">
         <v>105</v>
       </c>
-      <c r="D7" s="66" t="n">
+      <c r="D7" s="64" t="n">
         <v>112</v>
       </c>
-      <c r="E7" s="66" t="n">
+      <c r="E7" s="64" t="n">
         <v>85</v>
       </c>
-      <c r="F7" s="67" t="n">
+      <c r="F7" s="65" t="n">
         <f aca="false">INDEX(C7:E7,1,$B$4)</f>
         <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="68"/>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="C8" s="66" t="n">
+      <c r="C8" s="64" t="n">
         <v>110</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="64" t="n">
         <v>140</v>
       </c>
-      <c r="E8" s="66" t="n">
+      <c r="E8" s="64" t="n">
         <v>80</v>
       </c>
-      <c r="F8" s="67" t="n">
+      <c r="F8" s="65" t="n">
         <f aca="false">INDEX(C8:E8,1,$B$4)</f>
         <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68"/>
-      <c r="B9" s="65" t="s">
+      <c r="A9" s="66"/>
+      <c r="B9" s="63" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="66" t="n">
+      <c r="C9" s="64" t="n">
         <v>110</v>
       </c>
-      <c r="D9" s="66" t="n">
+      <c r="D9" s="64" t="n">
         <v>140</v>
       </c>
-      <c r="E9" s="66" t="n">
+      <c r="E9" s="64" t="n">
         <v>80</v>
       </c>
-      <c r="F9" s="67" t="n">
+      <c r="F9" s="65" t="n">
         <f aca="false">INDEX(C9:E9,1,$B$4)</f>
         <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="63" t="s">
         <v>283</v>
       </c>
       <c r="C10" s="55" t="n">
@@ -15247,13 +15242,13 @@
       <c r="E10" s="55" t="n">
         <v>0.015</v>
       </c>
-      <c r="F10" s="70" t="n">
+      <c r="F10" s="68" t="n">
         <f aca="false">INDEX(C10:E10,1,$B$4)</f>
         <v>0.026</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="68"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="56" t="s">
         <v>284</v>
       </c>
@@ -15266,13 +15261,13 @@
       <c r="E11" s="55" t="n">
         <v>0.005</v>
       </c>
-      <c r="F11" s="70" t="n">
+      <c r="F11" s="68" t="n">
         <f aca="false">INDEX(C11:E11,1,$B$4)</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="68"/>
+      <c r="A12" s="66"/>
       <c r="B12" s="56" t="s">
         <v>285</v>
       </c>
@@ -15285,13 +15280,13 @@
       <c r="E12" s="55" t="n">
         <v>0.005</v>
       </c>
-      <c r="F12" s="70" t="n">
+      <c r="F12" s="68" t="n">
         <f aca="false">INDEX(C12:E12,1,$B$4)</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="62" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="56" t="s">
@@ -15306,13 +15301,13 @@
       <c r="E13" s="55" t="n">
         <v>0.7</v>
       </c>
-      <c r="F13" s="70" t="n">
+      <c r="F13" s="68" t="n">
         <f aca="false">INDEX(C13:E13,1,$B$4)</f>
         <v>0.85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="68"/>
+      <c r="A14" s="66"/>
       <c r="B14" s="56" t="s">
         <v>284</v>
       </c>
@@ -15325,13 +15320,13 @@
       <c r="E14" s="55" t="n">
         <v>0.7</v>
       </c>
-      <c r="F14" s="70" t="n">
+      <c r="F14" s="68" t="n">
         <f aca="false">INDEX(C14:E14,1,$B$4)</f>
         <v>0.85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="68"/>
+      <c r="A15" s="66"/>
       <c r="B15" s="56" t="s">
         <v>285</v>
       </c>
@@ -15344,13 +15339,13 @@
       <c r="E15" s="55" t="n">
         <v>0.7</v>
       </c>
-      <c r="F15" s="70" t="n">
+      <c r="F15" s="68" t="n">
         <f aca="false">INDEX(C15:E15,1,$B$4)</f>
         <v>0.85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="62" t="s">
         <v>471</v>
       </c>
       <c r="B16" s="56" t="s">
@@ -15365,13 +15360,13 @@
       <c r="E16" s="55" t="n">
         <v>0.06</v>
       </c>
-      <c r="F16" s="70" t="n">
+      <c r="F16" s="68" t="n">
         <f aca="false">INDEX(C16:E16,1,$B$4)</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="68"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="56" t="s">
         <v>284</v>
       </c>
@@ -15384,13 +15379,13 @@
       <c r="E17" s="55" t="n">
         <v>0.04</v>
       </c>
-      <c r="F17" s="70" t="n">
+      <c r="F17" s="68" t="n">
         <f aca="false">INDEX(C17:E17,1,$B$4)</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="56" t="s">
         <v>285</v>
       </c>
@@ -15403,13 +15398,13 @@
       <c r="E18" s="55" t="n">
         <v>0.04</v>
       </c>
-      <c r="F18" s="70" t="n">
+      <c r="F18" s="68" t="n">
         <f aca="false">INDEX(C18:E18,1,$B$4)</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="62" t="s">
         <v>105</v>
       </c>
       <c r="B19" s="56" t="s">
@@ -15424,13 +15419,13 @@
       <c r="E19" s="55" t="n">
         <v>0.082</v>
       </c>
-      <c r="F19" s="70" t="n">
+      <c r="F19" s="68" t="n">
         <f aca="false">INDEX(C19:E19,1,$B$4)</f>
         <v>0.088</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="68"/>
+      <c r="A20" s="66"/>
       <c r="B20" s="56" t="s">
         <v>284</v>
       </c>
@@ -15443,13 +15438,13 @@
       <c r="E20" s="55" t="n">
         <v>0.08</v>
       </c>
-      <c r="F20" s="70" t="n">
+      <c r="F20" s="68" t="n">
         <f aca="false">INDEX(C20:E20,1,$B$4)</f>
         <v>0.09</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68"/>
+      <c r="A21" s="66"/>
       <c r="B21" s="56" t="s">
         <v>285</v>
       </c>
@@ -15462,162 +15457,162 @@
       <c r="E21" s="55" t="n">
         <v>0.083</v>
       </c>
-      <c r="F21" s="70" t="n">
+      <c r="F21" s="68" t="n">
         <f aca="false">INDEX(C21:E21,1,$B$4)</f>
         <v>0.093</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
+      <c r="A22" s="66"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="68"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="68"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="68"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="68"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="68"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="68"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="68"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="68"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="68"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="68"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="68"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="68"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="68"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="68"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="68"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="68"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -15635,7 +15630,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
@@ -15648,432 +15643,589 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="69" t="s">
         <v>473</v>
       </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="66"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="70" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="36" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
         <v>475</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="71"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="66" t="s">
         <v>476</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="36" t="s">
+      <c r="B6" s="72" t="n">
+        <f aca="false">Historical!F36</f>
+        <v>1781.7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="66" t="s">
         <v>477</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="B7" s="54" t="n">
+        <f aca="false">Historical!G47</f>
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="71" t="n">
-        <f aca="false">B36</f>
+      <c r="B8" s="73" t="n">
+        <f aca="false">Historical!F49</f>
+        <v>0.884877079711944</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="B9" s="74" t="n">
+        <f aca="false">B8*(1+B7)</f>
+        <v>0.906114129625031</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="66" t="s">
+        <v>480</v>
+      </c>
+      <c r="B10" s="75" t="n">
+        <f aca="false">Historical!F42-Historical!E42</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="66" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" s="75" t="n">
+        <f aca="false">Historical!G42-Historical!F42</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="66" t="s">
+        <v>482</v>
+      </c>
+      <c r="B12" s="54" t="n">
+        <f aca="false">Drivers!C9</f>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="76" t="n">
+        <f aca="false">B6*(1+B7)</f>
+        <v>1824.4608</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="66" t="s">
+        <v>483</v>
+      </c>
+      <c r="B14" s="76" t="n">
+        <f aca="false">B10*(1-Drivers!C36)*B9*B12</f>
+        <v>33.5035699428855</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="66" t="s">
+        <v>484</v>
+      </c>
+      <c r="B15" s="76" t="n">
+        <f aca="false">B11*Drivers!C36*B9*B12</f>
+        <v>30.8078804072511</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="62" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" s="76" t="n">
+        <f aca="false">B13+B14+B15</f>
         <v>1888.77225035014</v>
       </c>
-      <c r="C6" s="45" t="n">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="66" t="s">
+        <v>486</v>
+      </c>
+      <c r="B17" s="72" t="n">
         <f aca="false">Historical!G36</f>
         <v>1897.2</v>
       </c>
-      <c r="D6" s="30" t="n">
-        <f aca="false">IF(B6="","",C6-B6)</f>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="62" t="s">
+        <v>487</v>
+      </c>
+      <c r="B18" s="76" t="n">
+        <f aca="false">B17-B16</f>
         <v>8.42774964986324</v>
       </c>
-      <c r="E6" s="29" t="n">
-        <f aca="false">IF(OR(B6="",B6=0),"",D6/ABS(B6))</f>
-        <v>0.00446202534387136</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="45" t="n">
-        <f aca="false">Historical!G37</f>
-        <v>254</v>
-      </c>
-      <c r="D7" s="30" t="str">
-        <f aca="false">IF(B7="","",C7-B7)</f>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="68" t="n">
+        <f aca="false">B18/B17</f>
+        <v>0.00444220411652079</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="66" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" s="68" t="n">
+        <f aca="false">(B17-B13)/((B10*(1-Drivers!C36)+B11*Drivers!C36)*B9)</f>
+        <v>0.961388985373251</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="62" t="s">
+        <v>490</v>
+      </c>
+      <c r="B21" s="77" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="66"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="66"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="46" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36"/>
+      <c r="B25" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="78"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="25" t="str">
+        <f aca="false">IF(OR(B26="",C26=""),"",C26-B26)</f>
         <v/>
       </c>
-      <c r="E7" s="29" t="str">
-        <f aca="false">IF(OR(B7="",B7=0),"",D7/ABS(B7))</f>
+      <c r="E26" s="79" t="str">
+        <f aca="false">IF(D26="","",D26/ABS(B26))</f>
         <v/>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="45" t="n">
-        <f aca="false">Historical!G7</f>
-        <v>2151.2</v>
-      </c>
-      <c r="D8" s="30" t="str">
-        <f aca="false">IF(B8="","",C8-B8)</f>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="25" t="str">
+        <f aca="false">IF(OR(B27="",C27=""),"",C27-B27)</f>
         <v/>
       </c>
-      <c r="E8" s="29" t="str">
-        <f aca="false">IF(OR(B8="",B8=0),"",D8/ABS(B8))</f>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="25" t="str">
+        <f aca="false">IF(OR(B28="",C28=""),"",C28-B28)</f>
         <v/>
       </c>
-      <c r="F8" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="45" t="n">
-        <f aca="false">Historical!G24</f>
-        <v>187.5</v>
-      </c>
-      <c r="D9" s="30" t="str">
-        <f aca="false">IF(B9="","",C9-B9)</f>
+      <c r="E28" s="79" t="str">
+        <f aca="false">IF(D28="","",D28/ABS(B28))</f>
         <v/>
       </c>
-      <c r="E9" s="29" t="str">
-        <f aca="false">IF(OR(B9="",B9=0),"",D9/ABS(B9))</f>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="25" t="str">
+        <f aca="false">IF(OR(B29="",C29=""),"",C29-B29)</f>
         <v/>
       </c>
-      <c r="F9" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="45" t="n">
-        <f aca="false">Historical!G25</f>
-        <v>171.9</v>
-      </c>
-      <c r="D10" s="30" t="str">
-        <f aca="false">IF(B10="","",C10-B10)</f>
+      <c r="E29" s="79" t="str">
+        <f aca="false">IF(D29="","",D29/ABS(B29))</f>
         <v/>
       </c>
-      <c r="E10" s="29" t="str">
-        <f aca="false">IF(OR(B10="",B10=0),"",D10/ABS(B10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="45" t="n">
-        <f aca="false">Historical!G97</f>
-        <v>337</v>
-      </c>
-      <c r="D11" s="30" t="str">
-        <f aca="false">IF(B11="","",C11-B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="29" t="str">
-        <f aca="false">IF(OR(B11="",B11=0),"",D11/ABS(B11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>483</v>
-      </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="45" t="n">
-        <f aca="false">Historical!G117</f>
-        <v>-285.4</v>
-      </c>
-      <c r="D12" s="30" t="str">
-        <f aca="false">IF(B12="","",C12-B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="29" t="str">
-        <f aca="false">IF(OR(B12="",B12=0),"",D12/ABS(B12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="45" t="n">
-        <f aca="false">Historical!G61</f>
-        <v>70.8</v>
-      </c>
-      <c r="D13" s="30" t="str">
-        <f aca="false">IF(B13="","",C13-B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="29" t="str">
-        <f aca="false">IF(OR(B13="",B13=0),"",D13/ABS(B13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="57" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36" t="s">
-        <v>486</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>487</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>477</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="s">
-        <v>489</v>
-      </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="25" t="str">
-        <f aca="false">IF(OR(B18="",C18=""),"",C18-B18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="25" t="str">
-        <f aca="false">IF(OR(B19="",C19=""),"",C19-B19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
-        <v>490</v>
-      </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="25" t="str">
-        <f aca="false">IF(OR(B20="",C20=""),"",C20-B20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="25" t="str">
-        <f aca="false">IF(OR(B21="",C21=""),"",C21-B21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="73" t="s">
-        <v>492</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="56" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="68" t="s">
-        <v>494</v>
-      </c>
-      <c r="B26" s="74" t="n">
-        <f aca="false">Historical!F36</f>
-        <v>1781.7</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="68" t="s">
-        <v>495</v>
-      </c>
-      <c r="B27" s="54" t="n">
-        <f aca="false">Historical!G47</f>
-        <v>0.024</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="68" t="s">
-        <v>496</v>
-      </c>
-      <c r="B28" s="75" t="n">
-        <f aca="false">Historical!F49</f>
-        <v>0.884877079711944</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="68" t="s">
-        <v>497</v>
-      </c>
-      <c r="B29" s="76" t="n">
-        <f aca="false">B28*(1+B27)</f>
-        <v>0.906114129625031</v>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="68" t="s">
-        <v>498</v>
-      </c>
-      <c r="B30" s="77" t="n">
-        <f aca="false">Historical!F42-Historical!E42</f>
-        <v>87</v>
-      </c>
+      <c r="A30" s="66"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="68" t="s">
-        <v>499</v>
-      </c>
-      <c r="B31" s="77" t="n">
-        <f aca="false">Historical!G42-Historical!F42</f>
-        <v>80</v>
-      </c>
+      <c r="A31" s="66"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="68" t="s">
-        <v>500</v>
-      </c>
-      <c r="B32" s="54" t="n">
-        <f aca="false">Drivers!C9</f>
-        <v>0.85</v>
-      </c>
+      <c r="A32" s="66"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="68" t="s">
-        <v>299</v>
-      </c>
-      <c r="B33" s="78" t="n">
-        <f aca="false">B26*(1+B27)</f>
-        <v>1824.4608</v>
-      </c>
+      <c r="A33" s="66"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68" t="s">
-        <v>501</v>
-      </c>
-      <c r="B34" s="78" t="n">
-        <f aca="false">B30*(1-Drivers!C36)*B29*B32</f>
-        <v>33.5035699428855</v>
-      </c>
+      <c r="A34" s="66"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="68" t="s">
-        <v>502</v>
-      </c>
-      <c r="B35" s="78" t="n">
-        <f aca="false">B31*Drivers!C36*B29*B32</f>
-        <v>30.8078804072511</v>
-      </c>
+      <c r="A35" s="66"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="64" t="s">
-        <v>503</v>
-      </c>
-      <c r="B36" s="78" t="n">
-        <f aca="false">B33+B34+B35</f>
-        <v>1888.77225035014</v>
-      </c>
+      <c r="A36" s="66"/>
+      <c r="B36" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="68" t="s">
-        <v>504</v>
-      </c>
-      <c r="B37" s="74" t="n">
-        <f aca="false">Historical!G36</f>
-        <v>1897.2</v>
-      </c>
+      <c r="A37" s="66"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="64" t="s">
-        <v>505</v>
-      </c>
-      <c r="B38" s="78" t="n">
-        <f aca="false">B37-B36</f>
-        <v>8.42774964986324</v>
-      </c>
+      <c r="A38" s="66"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="64" t="s">
-        <v>477</v>
-      </c>
-      <c r="B39" s="70" t="n">
-        <f aca="false">B38/B37</f>
-        <v>0.00444220411652079</v>
-      </c>
+      <c r="A39" s="66"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="68" t="s">
-        <v>506</v>
-      </c>
-      <c r="B40" s="70" t="n">
-        <f aca="false">(B37-B33)/((B30*(1-Drivers!C36)+B31*Drivers!C36)*B29)</f>
-        <v>0.961388985373251</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="64" t="s">
-        <v>507</v>
-      </c>
-      <c r="B41" s="79" t="s">
-        <v>508</v>
-      </c>
+      <c r="A40" s="66"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="66"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="66"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="66"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="66"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="66"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="66"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="66"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="66"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="66"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="66"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="66"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="66"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="66"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="66"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="66"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="66"/>
+      <c r="H52" s="66"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="66"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
+      <c r="G53" s="66"/>
+      <c r="H53" s="66"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="66"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="66"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="66"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="66"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="66"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="66"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="66"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="66"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="66"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -16089,7 +16241,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
@@ -16099,17 +16251,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>510</v>
-      </c>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="80" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -16123,7 +16281,7 @@
         <v>129</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>131</v>
@@ -16171,10 +16329,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>0.19</v>
@@ -16194,7 +16352,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>146</v>
@@ -16222,110 +16380,110 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C9" s="80" t="n">
+        <v>507</v>
+      </c>
+      <c r="C9" s="81" t="n">
         <v>2.8</v>
       </c>
-      <c r="D9" s="80" t="n">
+      <c r="D9" s="81" t="n">
         <v>4.3</v>
       </c>
-      <c r="E9" s="80" t="n">
+      <c r="E9" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="80" t="n">
+      <c r="F9" s="81" t="n">
         <v>1.8</v>
       </c>
-      <c r="G9" s="80" t="n">
+      <c r="G9" s="81" t="n">
         <v>-2.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>518</v>
-      </c>
-      <c r="C10" s="80" t="n">
+        <v>508</v>
+      </c>
+      <c r="C10" s="81" t="n">
         <v>-1</v>
       </c>
-      <c r="D10" s="80" t="n">
+      <c r="D10" s="81" t="n">
         <v>-1</v>
       </c>
-      <c r="E10" s="80" t="n">
+      <c r="E10" s="81" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F10" s="80" t="n">
+      <c r="F10" s="81" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G10" s="80" t="n">
+      <c r="G10" s="81" t="n">
         <v>-1.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>519</v>
-      </c>
-      <c r="C11" s="80" t="n">
+        <v>509</v>
+      </c>
+      <c r="C11" s="81" t="n">
         <v>-3.6</v>
       </c>
-      <c r="D11" s="80" t="n">
+      <c r="D11" s="81" t="n">
         <v>-3.4</v>
       </c>
-      <c r="E11" s="80" t="n">
+      <c r="E11" s="81" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F11" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="80" t="n">
+      <c r="F11" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="C12" s="80" t="n">
+        <v>510</v>
+      </c>
+      <c r="C12" s="81" t="n">
         <v>1.2</v>
       </c>
-      <c r="D12" s="80" t="n">
+      <c r="D12" s="81" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="80" t="n">
+      <c r="E12" s="81" t="n">
         <v>0.2</v>
       </c>
-      <c r="F12" s="80" t="n">
+      <c r="F12" s="81" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G12" s="80" t="n">
+      <c r="G12" s="81" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>521</v>
-      </c>
-      <c r="C13" s="80" t="n">
+        <v>511</v>
+      </c>
+      <c r="C13" s="81" t="n">
         <v>0.2</v>
       </c>
-      <c r="D13" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="80" t="n">
+      <c r="D13" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>146</v>
@@ -16353,7 +16511,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>16</v>
@@ -16381,7 +16539,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>146</v>
@@ -16409,7 +16567,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>146</v>
@@ -16437,10 +16595,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C18" s="29" t="n">
         <f aca="false">C17-C7</f>
@@ -16465,7 +16623,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -16479,7 +16637,7 @@
         <v>129</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C21" s="21" t="s">
         <v>131</v>
@@ -16499,53 +16657,53 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="C22" s="80" t="n">
+        <v>520</v>
+      </c>
+      <c r="C22" s="81" t="n">
         <v>-18.9</v>
       </c>
-      <c r="D22" s="80" t="n">
+      <c r="D22" s="81" t="n">
         <v>-13.9</v>
       </c>
-      <c r="E22" s="80" t="n">
+      <c r="E22" s="81" t="n">
         <v>-17.7</v>
       </c>
-      <c r="F22" s="80" t="n">
+      <c r="F22" s="81" t="n">
         <v>-33.4</v>
       </c>
-      <c r="G22" s="80" t="n">
+      <c r="G22" s="81" t="n">
         <v>-24.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="C23" s="80" t="n">
+        <v>522</v>
+      </c>
+      <c r="C23" s="81" t="n">
         <v>-9.2</v>
       </c>
-      <c r="D23" s="80" t="n">
+      <c r="D23" s="81" t="n">
         <v>-14.1</v>
       </c>
-      <c r="E23" s="80" t="n">
+      <c r="E23" s="81" t="n">
         <v>-28.1</v>
       </c>
-      <c r="F23" s="80" t="n">
+      <c r="F23" s="81" t="n">
         <v>-17.1</v>
       </c>
-      <c r="G23" s="80" t="n">
+      <c r="G23" s="81" t="n">
         <v>-20.4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>146</v>
@@ -16573,7 +16731,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>146</v>
@@ -16601,10 +16759,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C26" s="45" t="n">
         <f aca="false">Historical!C93</f>
@@ -16629,7 +16787,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -16643,7 +16801,7 @@
         <v>129</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>131</v>
@@ -16663,12 +16821,12 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="C30" s="80" t="n">
+        <v>529</v>
+      </c>
+      <c r="C30" s="81" t="n">
         <v>2.3</v>
       </c>
       <c r="D30" s="30" t="n">
@@ -16690,76 +16848,76 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>541</v>
-      </c>
-      <c r="C31" s="80" t="n">
+        <v>531</v>
+      </c>
+      <c r="C31" s="81" t="n">
         <v>9.2</v>
       </c>
-      <c r="D31" s="80" t="n">
+      <c r="D31" s="81" t="n">
         <v>14.1</v>
       </c>
-      <c r="E31" s="80" t="n">
+      <c r="E31" s="81" t="n">
         <v>28.1</v>
       </c>
-      <c r="F31" s="80" t="n">
+      <c r="F31" s="81" t="n">
         <v>17.1</v>
       </c>
-      <c r="G31" s="80" t="n">
+      <c r="G31" s="81" t="n">
         <v>20.4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>543</v>
-      </c>
-      <c r="C32" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="80" t="n">
+        <v>533</v>
+      </c>
+      <c r="C32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="C33" s="80" t="n">
+        <v>535</v>
+      </c>
+      <c r="C33" s="81" t="n">
         <v>-1.5</v>
       </c>
-      <c r="D33" s="80" t="n">
+      <c r="D33" s="81" t="n">
         <v>2.2</v>
       </c>
-      <c r="E33" s="80" t="n">
+      <c r="E33" s="81" t="n">
         <v>0.3</v>
       </c>
-      <c r="F33" s="80" t="n">
+      <c r="F33" s="81" t="n">
         <v>0.8</v>
       </c>
-      <c r="G33" s="80" t="n">
+      <c r="G33" s="81" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>146</v>
@@ -16787,7 +16945,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>16</v>
@@ -16815,7 +16973,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>146</v>
@@ -16843,7 +17001,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>16</v>
@@ -16871,7 +17029,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="B39" s="18" t="s">
         <v>16</v>
@@ -16899,7 +17057,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="B40" s="18" t="s">
         <v>146</v>
@@ -16925,156 +17083,211 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
+    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="70" t="s">
+        <v>541</v>
+      </c>
+      <c r="B43" s="82"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+    </row>
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="83" t="s">
+        <v>542</v>
+      </c>
+      <c r="B44" s="83" t="s">
+        <v>543</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>544</v>
+      </c>
+      <c r="D44" s="83"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+    </row>
+    <row r="45" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="84" t="s">
+        <v>545</v>
+      </c>
+      <c r="B45" s="84" t="s">
+        <v>546</v>
+      </c>
+      <c r="C45" s="84" t="s">
+        <v>547</v>
+      </c>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="56" t="s">
+        <v>548</v>
+      </c>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="66"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="70" t="s">
+        <v>549</v>
+      </c>
+      <c r="B48" s="82"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="82"/>
+      <c r="F48" s="82"/>
+      <c r="G48" s="82"/>
+    </row>
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="83" t="s">
+        <v>550</v>
+      </c>
+      <c r="B49" s="83" t="s">
         <v>551</v>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36" t="s">
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+    </row>
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="85" t="s">
         <v>552</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B50" s="84" t="s">
         <v>553</v>
       </c>
-      <c r="C44" s="81" t="s">
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+    </row>
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="85" t="s">
         <v>554</v>
       </c>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-    </row>
-    <row r="45" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="79" t="s">
+      <c r="B51" s="84" t="s">
         <v>555</v>
       </c>
-      <c r="B45" s="79" t="s">
+      <c r="C51" s="84"/>
+      <c r="D51" s="84"/>
+      <c r="E51" s="84"/>
+      <c r="F51" s="84"/>
+      <c r="G51" s="84"/>
+    </row>
+    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="85" t="s">
         <v>556</v>
       </c>
-      <c r="C45" s="82" t="s">
+      <c r="B52" s="84" t="s">
         <v>557</v>
       </c>
-      <c r="D45" s="82"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
-    </row>
-    <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="83" t="s">
-        <v>558</v>
-      </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85"/>
-      <c r="F46" s="85"/>
-      <c r="G46" s="85"/>
-    </row>
-    <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="84"/>
-      <c r="B47" s="84"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-    </row>
-    <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="84"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-    </row>
-    <row r="49" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="84"/>
-      <c r="B49" s="84"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="85"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="s">
-        <v>560</v>
-      </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-    </row>
-    <row r="53" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="25" t="s">
-        <v>561</v>
-      </c>
-      <c r="B53" s="86" t="s">
-        <v>562</v>
-      </c>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-    </row>
-    <row r="54" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="25" t="s">
-        <v>563</v>
-      </c>
-      <c r="B54" s="86" t="s">
-        <v>564</v>
-      </c>
-      <c r="C54" s="86"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="86"/>
-    </row>
-    <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="25" t="s">
-        <v>565</v>
-      </c>
-      <c r="B55" s="86" t="s">
-        <v>566</v>
-      </c>
-      <c r="C55" s="86"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="66"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
+      <c r="G53" s="66"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="66"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="66"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18" t="s">
-        <v>567</v>
-      </c>
+      <c r="A56" s="66"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="66"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="66"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="66"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="66"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="66"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -17100,711 +17313,711 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="87" t="s">
-        <v>568</v>
+      <c r="A1" s="86" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="56" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="62" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>563</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>564</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>565</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>566</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>567</v>
+      </c>
+      <c r="I5" s="61" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="87" t="n">
+        <v>2262.2</v>
+      </c>
+      <c r="D6" s="87" t="n">
+        <v>2272.5</v>
+      </c>
+      <c r="E6" s="87" t="n">
+        <v>2280.2</v>
+      </c>
+      <c r="F6" s="87" t="n">
+        <v>2287.7</v>
+      </c>
+      <c r="G6" s="87" t="n">
+        <v>2297.7</v>
+      </c>
+      <c r="H6" s="87" t="n">
+        <v>2280.1</v>
+      </c>
+      <c r="I6" s="87" t="n">
+        <v>2283.6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="87" t="n">
+        <v>2357.2</v>
+      </c>
+      <c r="D7" s="87" t="n">
+        <v>2389.1</v>
+      </c>
+      <c r="E7" s="87" t="n">
+        <v>2412.6</v>
+      </c>
+      <c r="F7" s="87" t="n">
+        <v>2435.1</v>
+      </c>
+      <c r="G7" s="87" t="n">
+        <v>2466</v>
+      </c>
+      <c r="H7" s="87" t="n">
+        <v>2412</v>
+      </c>
+      <c r="I7" s="87" t="n">
+        <v>2421.1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="87" t="n">
+        <v>2456.4</v>
+      </c>
+      <c r="D8" s="87" t="n">
+        <v>2512.3</v>
+      </c>
+      <c r="E8" s="87" t="n">
+        <v>2553.6</v>
+      </c>
+      <c r="F8" s="87" t="n">
+        <v>2593.4</v>
+      </c>
+      <c r="G8" s="87" t="n">
+        <v>2648.8</v>
+      </c>
+      <c r="H8" s="87" t="n">
+        <v>2553</v>
+      </c>
+      <c r="I8" s="87" t="n">
+        <v>2566.8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="87" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="D9" s="87" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="E9" s="87" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="F9" s="87" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="G9" s="87" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="H9" s="87" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="I9" s="87" t="n">
+        <v>180.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="87" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="D10" s="87" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="E10" s="87" t="n">
+        <v>196</v>
+      </c>
+      <c r="F10" s="87" t="n">
+        <v>204.2</v>
+      </c>
+      <c r="G10" s="87" t="n">
+        <v>215.3</v>
+      </c>
+      <c r="H10" s="87" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="I10" s="87" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" s="87" t="n">
+        <v>193</v>
+      </c>
+      <c r="D11" s="87" t="n">
+        <v>206.2</v>
+      </c>
+      <c r="E11" s="87" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="F11" s="87" t="n">
+        <v>226</v>
+      </c>
+      <c r="G11" s="87" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="H11" s="87" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="I11" s="87" t="n">
+        <v>217.6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" s="87" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D12" s="87" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E12" s="87" t="n">
+        <v>82.4</v>
+      </c>
+      <c r="F12" s="87" t="n">
+        <v>86.9</v>
+      </c>
+      <c r="G12" s="87" t="n">
+        <v>93</v>
+      </c>
+      <c r="H12" s="87" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I12" s="87" t="n">
+        <v>84.6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="87" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="D13" s="87" t="n">
+        <v>77.1</v>
+      </c>
+      <c r="E13" s="87" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="F13" s="87" t="n">
+        <v>97.1</v>
+      </c>
+      <c r="G13" s="87" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="H13" s="87" t="n">
+        <v>87</v>
+      </c>
+      <c r="I13" s="87" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="87" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="D14" s="87" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="E14" s="87" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="F14" s="87" t="n">
+        <v>138</v>
+      </c>
+      <c r="G14" s="87" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="H14" s="87" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="I14" s="87" t="n">
+        <v>134.6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="66" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
+      <c r="B15" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="87" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D15" s="87" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="E15" s="87" t="n">
+        <v>82.9</v>
+      </c>
+      <c r="F15" s="87" t="n">
+        <v>87.4</v>
+      </c>
+      <c r="G15" s="87" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="H15" s="87" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="I15" s="87" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="66" t="s">
+        <v>569</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="87" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D16" s="87" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="E16" s="87" t="n">
+        <v>98.6</v>
+      </c>
+      <c r="F16" s="87" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="G16" s="87" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="H16" s="87" t="n">
+        <v>98.1</v>
+      </c>
+      <c r="I16" s="87" t="n">
+        <v>104.3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="66" t="s">
+        <v>569</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="87" t="n">
+        <v>93</v>
+      </c>
+      <c r="D17" s="87" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="E17" s="87" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="F17" s="87" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="G17" s="87" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="H17" s="87" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="I17" s="87" t="n">
+        <v>165.7</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="s">
         <v>571</v>
       </c>
-      <c r="B5" s="63" t="s">
-        <v>466</v>
-      </c>
-      <c r="C5" s="63" t="s">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61" t="s">
         <v>572</v>
       </c>
-      <c r="D5" s="63" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="66" t="s">
         <v>573</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="G21" s="79" t="n">
+        <v>0.898</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="66" t="s">
         <v>574</v>
       </c>
-      <c r="F5" s="63" t="s">
+      <c r="G22" s="79" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="66" t="s">
         <v>575</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G23" s="79" t="n">
+        <v>0.867</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="66" t="s">
         <v>576</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="G24" s="79" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="66" t="s">
         <v>577</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="G25" s="79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="62" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="C6" s="88" t="n">
-        <v>2262.2</v>
-      </c>
-      <c r="D6" s="88" t="n">
-        <v>2272.5</v>
-      </c>
-      <c r="E6" s="88" t="n">
-        <v>2280.2</v>
-      </c>
-      <c r="F6" s="88" t="n">
-        <v>2287.7</v>
-      </c>
-      <c r="G6" s="88" t="n">
-        <v>2297.7</v>
-      </c>
-      <c r="H6" s="88" t="n">
-        <v>2280.1</v>
-      </c>
-      <c r="I6" s="88" t="n">
-        <v>2283.6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" s="88" t="n">
-        <v>2357.2</v>
-      </c>
-      <c r="D7" s="88" t="n">
-        <v>2389.1</v>
-      </c>
-      <c r="E7" s="88" t="n">
-        <v>2412.6</v>
-      </c>
-      <c r="F7" s="88" t="n">
-        <v>2435.1</v>
-      </c>
-      <c r="G7" s="88" t="n">
-        <v>2466</v>
-      </c>
-      <c r="H7" s="88" t="n">
-        <v>2412</v>
-      </c>
-      <c r="I7" s="88" t="n">
-        <v>2421.1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="C8" s="88" t="n">
-        <v>2456.4</v>
-      </c>
-      <c r="D8" s="88" t="n">
-        <v>2512.3</v>
-      </c>
-      <c r="E8" s="88" t="n">
-        <v>2553.6</v>
-      </c>
-      <c r="F8" s="88" t="n">
-        <v>2593.4</v>
-      </c>
-      <c r="G8" s="88" t="n">
-        <v>2648.8</v>
-      </c>
-      <c r="H8" s="88" t="n">
-        <v>2553</v>
-      </c>
-      <c r="I8" s="88" t="n">
-        <v>2566.8</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="88" t="n">
-        <v>169.8</v>
-      </c>
-      <c r="D9" s="88" t="n">
-        <v>175.6</v>
-      </c>
-      <c r="E9" s="88" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="F9" s="88" t="n">
-        <v>184.1</v>
-      </c>
-      <c r="G9" s="88" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="H9" s="88" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="I9" s="88" t="n">
-        <v>180.2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" s="88" t="n">
-        <v>176.8</v>
-      </c>
-      <c r="D10" s="88" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="E10" s="88" t="n">
-        <v>196</v>
-      </c>
-      <c r="F10" s="88" t="n">
-        <v>204.2</v>
-      </c>
-      <c r="G10" s="88" t="n">
-        <v>215.3</v>
-      </c>
-      <c r="H10" s="88" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="I10" s="88" t="n">
-        <v>196.9</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="C11" s="88" t="n">
-        <v>193</v>
-      </c>
-      <c r="D11" s="88" t="n">
-        <v>206.2</v>
-      </c>
-      <c r="E11" s="88" t="n">
-        <v>216.1</v>
-      </c>
-      <c r="F11" s="88" t="n">
-        <v>226</v>
-      </c>
-      <c r="G11" s="88" t="n">
-        <v>239.6</v>
-      </c>
-      <c r="H11" s="88" t="n">
-        <v>216.2</v>
-      </c>
-      <c r="I11" s="88" t="n">
-        <v>217.6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="B12" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="88" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="D12" s="88" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="E12" s="88" t="n">
-        <v>82.4</v>
-      </c>
-      <c r="F12" s="88" t="n">
-        <v>86.9</v>
-      </c>
-      <c r="G12" s="88" t="n">
-        <v>93</v>
-      </c>
-      <c r="H12" s="88" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="I12" s="88" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="61" t="s">
+        <v>366</v>
+      </c>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61" t="s">
+        <v>579</v>
+      </c>
+      <c r="E28" s="61" t="s">
+        <v>580</v>
+      </c>
+      <c r="F28" s="61" t="s">
+        <v>581</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="87" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="E29" s="87" t="n">
+        <v>244.2</v>
+      </c>
+      <c r="F29" s="87" t="n">
+        <v>53</v>
+      </c>
+      <c r="G29" s="87" t="n">
+        <v>74.9</v>
+      </c>
+      <c r="H29" s="87" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="66" t="s">
+        <v>294</v>
+      </c>
+      <c r="D30" s="87" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="E30" s="87" t="n">
+        <v>228</v>
+      </c>
+      <c r="F30" s="87" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G30" s="87" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="H30" s="87" t="n">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="66" t="s">
+        <v>471</v>
+      </c>
+      <c r="D31" s="87" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="E31" s="87" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="F31" s="87" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G31" s="87" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="H31" s="87" t="n">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="87" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="E32" s="87" t="n">
+        <v>220</v>
+      </c>
+      <c r="F32" s="87" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G32" s="87" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H32" s="87" t="n">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="87" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="E33" s="87" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="F33" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="87" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="H33" s="87" t="n">
+        <v>85.9</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="66" t="s">
+        <v>584</v>
+      </c>
+      <c r="D34" s="87" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="E34" s="87" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="F34" s="87" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G34" s="87" t="n">
+        <v>93.9</v>
+      </c>
+      <c r="H34" s="87" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="87" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="E35" s="87" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="F35" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="87" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="H35" s="87" t="n">
+        <v>85.4</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="66" t="s">
+        <v>387</v>
+      </c>
+      <c r="D36" s="87" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="E36" s="87" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="F36" s="87" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G36" s="87" t="n">
         <v>84.6</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="88" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D13" s="88" t="n">
-        <v>77.1</v>
-      </c>
-      <c r="E13" s="88" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F13" s="88" t="n">
-        <v>97.1</v>
-      </c>
-      <c r="G13" s="88" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="H13" s="88" t="n">
-        <v>87</v>
-      </c>
-      <c r="I13" s="88" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="68" t="s">
-        <v>260</v>
-      </c>
-      <c r="B14" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="88" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="D14" s="88" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="E14" s="88" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="F14" s="88" t="n">
-        <v>138</v>
-      </c>
-      <c r="G14" s="88" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="H14" s="88" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="I14" s="88" t="n">
-        <v>134.6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="68" t="s">
-        <v>484</v>
-      </c>
-      <c r="B15" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="88" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="D15" s="88" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="E15" s="88" t="n">
-        <v>82.9</v>
-      </c>
-      <c r="F15" s="88" t="n">
-        <v>87.4</v>
-      </c>
-      <c r="G15" s="88" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="H15" s="88" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="I15" s="88" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="68" t="s">
-        <v>484</v>
-      </c>
-      <c r="B16" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="88" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="D16" s="88" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="E16" s="88" t="n">
-        <v>98.6</v>
-      </c>
-      <c r="F16" s="88" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="G16" s="88" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="H16" s="88" t="n">
-        <v>98.1</v>
-      </c>
-      <c r="I16" s="88" t="n">
-        <v>104.3</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="68" t="s">
-        <v>484</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="88" t="n">
-        <v>93</v>
-      </c>
-      <c r="D17" s="88" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="E17" s="88" t="n">
-        <v>153.3</v>
-      </c>
-      <c r="F17" s="88" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="G17" s="88" t="n">
-        <v>209.8</v>
-      </c>
-      <c r="H17" s="88" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="I17" s="88" t="n">
-        <v>165.7</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="s">
-        <v>580</v>
-      </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="s">
-        <v>582</v>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.898</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="s">
-        <v>583</v>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68" t="s">
-        <v>584</v>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.867</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="68" t="s">
+      <c r="H36" s="87" t="n">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="87" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="E37" s="87" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="F37" s="87" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G37" s="87" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H37" s="87" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="62" t="s">
         <v>585</v>
       </c>
-      <c r="G24" s="89" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="68" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="88" t="s">
         <v>586</v>
       </c>
-      <c r="G25" s="89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="64" t="s">
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="88"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="88" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="63" t="s">
-        <v>366</v>
-      </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63" t="s">
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="88" t="s">
         <v>588</v>
       </c>
-      <c r="E28" s="63" t="s">
-        <v>589</v>
-      </c>
-      <c r="F28" s="63" t="s">
-        <v>590</v>
-      </c>
-      <c r="G28" s="63" t="s">
-        <v>591</v>
-      </c>
-      <c r="H28" s="63" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="88" t="n">
-        <v>191.1</v>
-      </c>
-      <c r="E29" s="88" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="F29" s="88" t="n">
-        <v>53</v>
-      </c>
-      <c r="G29" s="88" t="n">
-        <v>74.9</v>
-      </c>
-      <c r="H29" s="88" t="n">
-        <v>95.2</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="68" t="s">
-        <v>294</v>
-      </c>
-      <c r="D30" s="88" t="n">
-        <v>205.2</v>
-      </c>
-      <c r="E30" s="88" t="n">
-        <v>228</v>
-      </c>
-      <c r="F30" s="88" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G30" s="88" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="H30" s="88" t="n">
-        <v>87.3</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="68" t="s">
-        <v>471</v>
-      </c>
-      <c r="D31" s="88" t="n">
-        <v>214.3</v>
-      </c>
-      <c r="E31" s="88" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="F31" s="88" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G31" s="88" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="H31" s="88" t="n">
-        <v>86.4</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="88" t="n">
-        <v>214.7</v>
-      </c>
-      <c r="E32" s="88" t="n">
-        <v>220</v>
-      </c>
-      <c r="F32" s="88" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G32" s="88" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="H32" s="88" t="n">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="68" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="88" t="n">
-        <v>214.6</v>
-      </c>
-      <c r="E33" s="88" t="n">
-        <v>219.6</v>
-      </c>
-      <c r="F33" s="88" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="88" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="H33" s="88" t="n">
-        <v>85.9</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="68" t="s">
-        <v>483</v>
-      </c>
-      <c r="D34" s="88" t="n">
-        <v>218.5</v>
-      </c>
-      <c r="E34" s="88" t="n">
-        <v>216.3</v>
-      </c>
-      <c r="F34" s="88" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="G34" s="88" t="n">
-        <v>93.9</v>
-      </c>
-      <c r="H34" s="88" t="n">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="88" t="n">
-        <v>216.7</v>
-      </c>
-      <c r="E35" s="88" t="n">
-        <v>218.6</v>
-      </c>
-      <c r="F35" s="88" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="88" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="H35" s="88" t="n">
-        <v>85.4</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="68" t="s">
-        <v>387</v>
-      </c>
-      <c r="D36" s="88" t="n">
-        <v>217.9</v>
-      </c>
-      <c r="E36" s="88" t="n">
-        <v>217.4</v>
-      </c>
-      <c r="F36" s="88" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G36" s="88" t="n">
-        <v>84.6</v>
-      </c>
-      <c r="H36" s="88" t="n">
-        <v>85.5</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="88" t="n">
-        <v>217.7</v>
-      </c>
-      <c r="E37" s="88" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="F37" s="88" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G37" s="88" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="H37" s="88" t="n">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="64" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="90" t="s">
-        <v>594</v>
-      </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="90"/>
-      <c r="F40" s="90"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-    </row>
-    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="90" t="s">
-        <v>595</v>
-      </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-    </row>
-    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="90" t="s">
-        <v>596</v>
-      </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
-      <c r="G42" s="90"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="90"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="3">
